--- a/exports/CROMPTON_full_report.xlsx
+++ b/exports/CROMPTON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.53</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>434.5</v>
+        <v>421.85</v>
       </c>
       <c r="I2" t="n">
         <v>428.053538187835</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.71</v>
+        <v>-4.57</v>
       </c>
       <c r="L2" t="n">
         <v>5.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44607.55208333334</v>
+        <v>44608.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>380.85</v>
+        <v>395.5</v>
       </c>
       <c r="I3" t="n">
         <v>389.1277742971643</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K3" t="n">
-        <v>9.720000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="L3" t="n">
         <v>2.56</v>
       </c>
       <c r="M3" t="n">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="N3" t="n">
-        <v>3.14</v>
+        <v>4.46</v>
       </c>
       <c r="O3" t="n">
         <v>-3.12</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.82</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>401.35</v>
+        <v>385.9</v>
       </c>
       <c r="I4" t="n">
         <v>388.6585146944134</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>1.48</v>
+        <v>-2.43</v>
       </c>
       <c r="L4" t="n">
         <v>6.31</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.41</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>347.25</v>
+        <v>352.5</v>
       </c>
       <c r="I5" t="n">
         <v>347.5579392479402</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>87</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>10.02</v>
+        <v>8.66</v>
       </c>
       <c r="L5" t="n">
         <v>6.79</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>7.78</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44722.38541666666</v>
+        <v>44722.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>344.75</v>
+        <v>341.4</v>
       </c>
       <c r="I6" t="n">
         <v>342.8331658557557</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2</v>
+        <v>-3.15</v>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>3.66</v>
       </c>
       <c r="M6" t="n">
         <v>0.93</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>6.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44735.55208333334</v>
+        <v>44736.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>332.5</v>
+        <v>341.8</v>
       </c>
       <c r="I7" t="n">
         <v>338.4411145123333</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>2.61</v>
+        <v>-0.12</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -840,7 +923,7 @@
         <v>0.93</v>
       </c>
       <c r="N7" t="n">
-        <v>2.31</v>
+        <v>3.16</v>
       </c>
       <c r="O7" t="n">
         <v>-1.5</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44764.38541666666</v>
+        <v>44764.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>387.2</v>
+        <v>374</v>
       </c>
       <c r="I8" t="n">
         <v>374.897972809373</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>13.28</v>
+        <v>9.42</v>
       </c>
       <c r="L8" t="n">
         <v>3.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44790.55208333334</v>
+        <v>44791.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>391.25</v>
+        <v>397.3</v>
       </c>
       <c r="I9" t="n">
         <v>393.7856063304893</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.61</v>
+        <v>-6.23</v>
       </c>
       <c r="L9" t="n">
         <v>8.289999999999999</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="I10" t="n">
         <v>399.4637205169414</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K10" t="n">
-        <v>1.69</v>
+        <v>0.43</v>
       </c>
       <c r="L10" t="n">
         <v>3.34</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.7</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44880.55208333334</v>
+        <v>44881.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>367</v>
+        <v>372.9</v>
       </c>
       <c r="I11" t="n">
         <v>370.7818085177132</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K11" t="n">
-        <v>8.02</v>
+        <v>6.54</v>
       </c>
       <c r="L11" t="n">
         <v>6.42</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.68</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44901.55208333334</v>
+        <v>44902.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>362</v>
+        <v>350.05</v>
       </c>
       <c r="I12" t="n">
         <v>355.6359388932132</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.92</v>
+        <v>-6.13</v>
       </c>
       <c r="L12" t="n">
-        <v>4.21</v>
+        <v>6.89</v>
       </c>
       <c r="M12" t="n">
         <v>0.36</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.2</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44950.38541666666</v>
+        <v>44950.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>335.65</v>
+        <v>338.9</v>
       </c>
       <c r="I13" t="n">
         <v>337.7670732030951</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K13" t="n">
-        <v>4.11</v>
+        <v>3.19</v>
       </c>
       <c r="L13" t="n">
         <v>3.96</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>5.08</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>328.4</v>
+        <v>319.25</v>
       </c>
       <c r="I14" t="n">
         <v>321.6960036349437</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.1</v>
+        <v>-5.8</v>
       </c>
       <c r="L14" t="n">
-        <v>3.92</v>
+        <v>6.34</v>
       </c>
       <c r="M14" t="n">
         <v>0.49</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.8</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44988.38541666666</v>
+        <v>44988.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>310.55</v>
+        <v>311.5</v>
       </c>
       <c r="I15" t="n">
         <v>311.4158037122512</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="L15" t="n">
         <v>6.19</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>4.58</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44994.38541666666</v>
+        <v>44994.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>305.4</v>
+        <v>299.9</v>
       </c>
       <c r="I16" t="n">
         <v>300.1740557415422</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.96</v>
+        <v>-3.72</v>
       </c>
       <c r="L16" t="n">
-        <v>2.54</v>
+        <v>4.03</v>
       </c>
       <c r="M16" t="n">
         <v>0.14</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.04</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>296</v>
+        <v>300.2</v>
       </c>
       <c r="I17" t="n">
         <v>297.0168472997497</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3</v>
+        <v>-0.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.92</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>6.21</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45040.55208333334</v>
+        <v>45041.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>294.25</v>
+        <v>260</v>
       </c>
       <c r="I18" t="n">
         <v>284.7675075346588</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.98</v>
+        <v>-13.39</v>
       </c>
       <c r="L18" t="n">
-        <v>4.23</v>
+        <v>14.86</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>4.84</v>
       </c>
       <c r="N18" t="n">
-        <v>2.12</v>
+        <v>11.61</v>
       </c>
       <c r="O18" t="n">
         <v>2.88</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.81</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45065.55208333334</v>
+        <v>45068.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>254.55</v>
+        <v>262.65</v>
       </c>
       <c r="I19" t="n">
         <v>262.2793103441441</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>-1.02</v>
       </c>
       <c r="L19" t="n">
         <v>7.69</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.34</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>299.75</v>
+        <v>283.75</v>
       </c>
       <c r="I20" t="n">
         <v>292.6478478880223</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>86</v>
       </c>
       <c r="K20" t="n">
-        <v>14.13</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>2.46</v>
@@ -1581,7 +1820,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>2.73</v>
+        <v>5.89</v>
       </c>
       <c r="O20" t="n">
         <v>2.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>9.83</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="I21" t="n">
         <v>302.1627391909874</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.02</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>5.73</v>
+        <v>11.49</v>
       </c>
       <c r="M21" t="n">
-        <v>0.87</v>
+        <v>2.68</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>3.54</v>
       </c>
       <c r="O21" t="n">
         <v>-5.89</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.13</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>306</v>
+        <v>303.55</v>
       </c>
       <c r="I22" t="n">
         <v>305.1055541203076</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.65</v>
+        <v>-1.44</v>
       </c>
       <c r="L22" t="n">
         <v>3.46</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.3</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45196.55208333334</v>
+        <v>45197.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>299.35</v>
+        <v>307.65</v>
       </c>
       <c r="I23" t="n">
         <v>306.4656967104528</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>1.38</v>
+        <v>-1.35</v>
       </c>
       <c r="L23" t="n">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="M23" t="n">
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.15</v>
+        <v>2.22</v>
       </c>
       <c r="O23" t="n">
         <v>-0.26</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.7</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>300.25</v>
+        <v>294.3</v>
       </c>
       <c r="I24" t="n">
         <v>295.7348419615952</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.41</v>
+        <v>-4.34</v>
       </c>
       <c r="L24" t="n">
-        <v>2.86</v>
+        <v>4.37</v>
       </c>
       <c r="M24" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="N24" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="O24" t="n">
         <v>2.22</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>5.49</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45250.55208333334</v>
+        <v>45251.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>287.9</v>
+        <v>290.2</v>
       </c>
       <c r="I25" t="n">
         <v>289.3686567663456</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K25" t="n">
-        <v>2.17</v>
+        <v>1.39</v>
       </c>
       <c r="L25" t="n">
         <v>3.57</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.08</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>292</v>
+        <v>288.35</v>
       </c>
       <c r="I26" t="n">
         <v>290.4709679654532</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K26" t="n">
-        <v>0.62</v>
+        <v>-0.64</v>
       </c>
       <c r="L26" t="n">
         <v>3.41</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45279.55208333334</v>
+        <v>45280.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>296.5</v>
+        <v>305.35</v>
       </c>
       <c r="I27" t="n">
         <v>300.2999956257153</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.83</v>
+        <v>-5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>3.47</v>
+        <v>6.75</v>
       </c>
       <c r="M27" t="n">
         <v>0.46</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.08</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>316.4</v>
+        <v>309.5</v>
       </c>
       <c r="I28" t="n">
         <v>310.8902737529116</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K28" t="n">
-        <v>3.62</v>
+        <v>1.36</v>
       </c>
       <c r="L28" t="n">
         <v>5.03</v>
@@ -2037,7 +2372,7 @@
         <v>0.98</v>
       </c>
       <c r="N28" t="n">
-        <v>1.19</v>
+        <v>2.18</v>
       </c>
       <c r="O28" t="n">
         <v>-0.17</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>5.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45352.38541666666</v>
+        <v>45355.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>294.7</v>
+        <v>298.35</v>
       </c>
       <c r="I29" t="n">
         <v>295.8721437028208</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K29" t="n">
-        <v>4.78</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
         <v>2.15</v>
       </c>
       <c r="M29" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="N29" t="n">
         <v>2.66</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>4.27</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>286.35</v>
+        <v>281.1</v>
       </c>
       <c r="I30" t="n">
         <v>285.6140235605577</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.02</v>
+        <v>-5.78</v>
       </c>
       <c r="L30" t="n">
-        <v>4.39</v>
+        <v>5.88</v>
       </c>
       <c r="M30" t="n">
         <v>0.02</v>
       </c>
       <c r="N30" t="n">
-        <v>1.53</v>
+        <v>2.97</v>
       </c>
       <c r="O30" t="n">
         <v>1.75</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.66</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>270.5</v>
+        <v>281.45</v>
       </c>
       <c r="I31" t="n">
         <v>279.1537205322924</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K31" t="n">
-        <v>3.77</v>
+        <v>-0.12</v>
       </c>
       <c r="L31" t="n">
         <v>2.95</v>
@@ -2208,7 +2579,7 @@
         <v>1.49</v>
       </c>
       <c r="N31" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
         <v>-2.97</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.89</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45471.38541666666</v>
+        <v>45471.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>410.25</v>
+        <v>405.75</v>
       </c>
       <c r="I32" t="n">
         <v>405.8046623827079</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>87</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>45.76</v>
+        <v>44.16</v>
       </c>
       <c r="L32" t="n">
         <v>3.8</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.98</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45484.55208333334</v>
+        <v>45485.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>425</v>
+        <v>435.05</v>
       </c>
       <c r="I33" t="n">
         <v>431.0377455117988</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.74</v>
+        <v>-7.22</v>
       </c>
       <c r="L33" t="n">
         <v>8.92</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>6.96</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45510.38541666666</v>
+        <v>45510.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>424.6</v>
+        <v>415.8</v>
       </c>
       <c r="I34" t="n">
         <v>421.6105067032059</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.4</v>
+        <v>-4.42</v>
       </c>
       <c r="L34" t="n">
-        <v>4.38</v>
+        <v>4.6</v>
       </c>
       <c r="M34" t="n">
         <v>2.56</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>9.44</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>454.5</v>
+        <v>466.25</v>
       </c>
       <c r="I35" t="n">
         <v>455.0549261014274</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.31</v>
+        <v>-12.13</v>
       </c>
       <c r="L35" t="n">
-        <v>10.63</v>
+        <v>12.73</v>
       </c>
       <c r="M35" t="n">
         <v>1.38</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>7.84</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>452.8</v>
+        <v>449.45</v>
       </c>
       <c r="I36" t="n">
         <v>449.9684218197015</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.88</v>
+        <v>-3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>3.34</v>
+        <v>3.99</v>
       </c>
       <c r="M36" t="n">
         <v>1.33</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.39</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>397.55</v>
+        <v>402</v>
       </c>
       <c r="I37" t="n">
         <v>401.7877819430372</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>11.55</v>
+        <v>10.56</v>
       </c>
       <c r="L37" t="n">
         <v>2.4</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45610.38541666666</v>
+        <v>45610.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>376.6</v>
+        <v>371.4</v>
       </c>
       <c r="I38" t="n">
         <v>375.1759069635258</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.32</v>
+        <v>-7.61</v>
       </c>
       <c r="L38" t="n">
-        <v>7.06</v>
+        <v>8.01</v>
       </c>
       <c r="M38" t="n">
         <v>0.73</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>393.1</v>
+        <v>403.25</v>
       </c>
       <c r="I39" t="n">
         <v>401.1283711631162</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-5.84</v>
+        <v>-8.58</v>
       </c>
       <c r="L39" t="n">
-        <v>7.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M39" t="n">
         <v>2.05</v>
       </c>
       <c r="N39" t="n">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="O39" t="n">
         <v>-3.36</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.97</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45643.38541666666</v>
+        <v>45643.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>400.25</v>
+        <v>396.55</v>
       </c>
       <c r="I40" t="n">
         <v>398.4706832654227</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.74</v>
+        <v>-1.66</v>
       </c>
       <c r="L40" t="n">
         <v>2.17</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.65</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>342.35</v>
+        <v>362</v>
       </c>
       <c r="I41" t="n">
         <v>357.1743433093592</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>45</v>
+        <v>45.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>13.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L41" t="n">
         <v>1.36</v>
@@ -2778,7 +3269,7 @@
         <v>1.14</v>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="O41" t="n">
         <v>-2.38</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>9.85</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>349.2</v>
+        <v>343.5</v>
       </c>
       <c r="I42" t="n">
         <v>344.8612817055128</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.54</v>
+        <v>-5.11</v>
       </c>
       <c r="L42" t="n">
         <v>6.4</v>
       </c>
       <c r="M42" t="n">
-        <v>0.46</v>
+        <v>1.2</v>
       </c>
       <c r="N42" t="n">
         <v>4.46</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>7.95</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45720.55208333334</v>
+        <v>45721.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>329.8</v>
+        <v>343.6</v>
       </c>
       <c r="I43" t="n">
         <v>342.9421888772013</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>3.99</v>
+        <v>-0.03</v>
       </c>
       <c r="L43" t="n">
         <v>2.65</v>
@@ -2892,7 +3407,7 @@
         <v>1.63</v>
       </c>
       <c r="N43" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>-1.45</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>9.81</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>345.5</v>
+        <v>335.9</v>
       </c>
       <c r="I44" t="n">
         <v>343.835477305472</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K44" t="n">
-        <v>0.55</v>
+        <v>-2.24</v>
       </c>
       <c r="L44" t="n">
         <v>5.03</v>
       </c>
       <c r="M44" t="n">
-        <v>0.86</v>
+        <v>2.43</v>
       </c>
       <c r="N44" t="n">
         <v>3.99</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.84</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45768.55208333334</v>
+        <v>45769.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>340.1</v>
+        <v>350.4</v>
       </c>
       <c r="I45" t="n">
         <v>340.6883787194145</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.25</v>
+        <v>-4.32</v>
       </c>
       <c r="L45" t="n">
-        <v>2.89</v>
+        <v>4.88</v>
       </c>
       <c r="M45" t="n">
         <v>4.49</v>
       </c>
       <c r="N45" t="n">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="O45" t="n">
         <v>-2.91</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>7.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>336.85</v>
+        <v>324.05</v>
       </c>
       <c r="I46" t="n">
         <v>332.4954765691887</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K46" t="n">
-        <v>-3.87</v>
+        <v>-7.52</v>
       </c>
       <c r="L46" t="n">
-        <v>6.21</v>
+        <v>7.73</v>
       </c>
       <c r="M46" t="n">
-        <v>0.08</v>
+        <v>0.39</v>
       </c>
       <c r="N46" t="n">
-        <v>2.35</v>
+        <v>4.41</v>
       </c>
       <c r="O46" t="n">
         <v>3.7</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45792.55208333334</v>
+        <v>45793.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>327.35</v>
+        <v>350.4</v>
       </c>
       <c r="I47" t="n">
         <v>342.4337525559212</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.02</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>4.77</v>
+        <v>8.58</v>
       </c>
       <c r="M47" t="n">
-        <v>2.92</v>
+        <v>3.67</v>
       </c>
       <c r="N47" t="n">
-        <v>4.05</v>
+        <v>7.33</v>
       </c>
       <c r="O47" t="n">
         <v>-4.41</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>8.74</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>344.15</v>
+        <v>342.6</v>
       </c>
       <c r="I48" t="n">
         <v>343.6817793896742</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.78</v>
+        <v>-2.23</v>
       </c>
       <c r="L48" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="M48" t="n">
-        <v>0.89</v>
+        <v>2.08</v>
       </c>
       <c r="N48" t="n">
         <v>2.45</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>3.56</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45833.38541666666</v>
+        <v>45833.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>352.55</v>
+        <v>355.05</v>
       </c>
       <c r="I49" t="n">
         <v>353.9850006188582</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.9</v>
+        <v>-3.63</v>
       </c>
       <c r="L49" t="n">
-        <v>3.52</v>
+        <v>3.84</v>
       </c>
       <c r="M49" t="n">
         <v>1.04</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>4.41</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45846.38541666666</v>
+        <v>45846.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>346.5</v>
+        <v>343.15</v>
       </c>
       <c r="I50" t="n">
         <v>344.8537098694094</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.41</v>
+        <v>-3.35</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="M50" t="n">
         <v>0.27</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>4.65</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45853.38541666666</v>
+        <v>45853.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="I51" t="n">
         <v>349.2617843898549</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.25</v>
+        <v>-2.29</v>
       </c>
       <c r="L51" t="n">
-        <v>1.05</v>
+        <v>2.91</v>
       </c>
       <c r="M51" t="n">
         <v>0.71</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>4.83</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45860.38541666666</v>
+        <v>45860.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>337</v>
+        <v>336.25</v>
       </c>
       <c r="I52" t="n">
         <v>336.762012710364</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.99</v>
+        <v>-4.2</v>
       </c>
       <c r="L52" t="n">
         <v>5.11</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>3.95</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45898.55208333334</v>
+        <v>45901.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>330.05</v>
+        <v>334.15</v>
       </c>
       <c r="I53" t="n">
         <v>331.0661571564568</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K53" t="n">
-        <v>1.84</v>
+        <v>0.62</v>
       </c>
       <c r="L53" t="n">
         <v>2.01</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>321.95</v>
+        <v>320.15</v>
       </c>
       <c r="I54" t="n">
         <v>321.0578227799103</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.65</v>
+        <v>-4.19</v>
       </c>
       <c r="L54" t="n">
-        <v>3.94</v>
+        <v>4.65</v>
       </c>
       <c r="M54" t="n">
         <v>0.36</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.47</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45951.57291666666</v>
+        <v>45953.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>288.65</v>
+        <v>292.4</v>
       </c>
       <c r="I55" t="n">
         <v>291.5260125888507</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>41.1875</v>
+        <v>43</v>
       </c>
       <c r="K55" t="n">
-        <v>9.84</v>
+        <v>8.67</v>
       </c>
       <c r="L55" t="n">
         <v>1.64</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>4.55</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45961.38541666666</v>
+        <v>45961.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>284.15</v>
+        <v>282.85</v>
       </c>
       <c r="I56" t="n">
         <v>283.0891667125519</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.82</v>
+        <v>-3.27</v>
       </c>
       <c r="L56" t="n">
-        <v>3.11</v>
+        <v>3.57</v>
       </c>
       <c r="M56" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N56" t="n">
         <v>1.56</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>3.92</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46010.55208333334</v>
+        <v>46013.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>256.5</v>
+        <v>259.65</v>
       </c>
       <c r="I57" t="n">
         <v>259.2260548861422</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>49</v>
+        <v>51.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>9.32</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L57" t="n">
         <v>1.24</v>
       </c>
       <c r="M57" t="n">
-        <v>0.87</v>
+        <v>1.35</v>
       </c>
       <c r="N57" t="n">
         <v>3.04</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.7</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>251.45</v>
+        <v>244.4</v>
       </c>
       <c r="I58" t="n">
         <v>248.851426885936</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K58" t="n">
-        <v>-3.16</v>
+        <v>-5.87</v>
       </c>
       <c r="L58" t="n">
-        <v>4.87</v>
+        <v>6.07</v>
       </c>
       <c r="M58" t="n">
         <v>0.2</v>
       </c>
       <c r="N58" t="n">
-        <v>2.43</v>
+        <v>3.36</v>
       </c>
       <c r="O58" t="n">
         <v>0.9</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>6.88</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>232.5</v>
+        <v>243.48</v>
       </c>
       <c r="I59" t="n">
         <v>234.3171360830677</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K59" t="n">
-        <v>4.87</v>
+        <v>0.38</v>
       </c>
       <c r="L59" t="n">
         <v>2.84</v>
@@ -3804,7 +4511,7 @@
         <v>3.73</v>
       </c>
       <c r="N59" t="n">
-        <v>2.64</v>
+        <v>5.38</v>
       </c>
       <c r="O59" t="n">
         <v>-3.36</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>10.04</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>256.59</v>
+        <v>250.6</v>
       </c>
       <c r="I60" t="n">
         <v>255.8228425275958</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K60" t="n">
-        <v>5.38</v>
+        <v>2.92</v>
       </c>
       <c r="L60" t="n">
         <v>4.67</v>
       </c>
       <c r="M60" t="n">
-        <v>0.5600000000000001</v>
+        <v>3.74</v>
       </c>
       <c r="N60" t="n">
         <v>2.24</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>6.56</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>234</v>
+        <v>246.79</v>
       </c>
       <c r="I61" t="n">
         <v>242.7727837661565</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>6.62</v>
+        <v>1.52</v>
       </c>
       <c r="L61" t="n">
         <v>2.31</v>
       </c>
       <c r="M61" t="n">
-        <v>2.1</v>
+        <v>3.42</v>
       </c>
       <c r="N61" t="n">
-        <v>3.24</v>
+        <v>4.91</v>
       </c>
       <c r="O61" t="n">
         <v>-0.07000000000000001</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>280.55</v>
+        <v>275.1</v>
       </c>
       <c r="I62" t="n">
         <v>278.6896662886115</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>51.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K62" t="n">
-        <v>13.68</v>
+        <v>11.47</v>
       </c>
       <c r="L62" t="n">
         <v>5.09</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>8.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>265</v>
+        <v>275.45</v>
       </c>
       <c r="I63" t="n">
         <v>269.0689414756154</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K63" t="n">
-        <v>3.67</v>
+        <v>-0.13</v>
       </c>
       <c r="L63" t="n">
         <v>3.18</v>
@@ -4032,7 +4787,7 @@
         <v>1.76</v>
       </c>
       <c r="N63" t="n">
-        <v>3.79</v>
+        <v>4.15</v>
       </c>
       <c r="O63" t="n">
         <v>-2.33</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>8.43</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>264.95</v>
+        <v>259</v>
       </c>
       <c r="I64" t="n">
         <v>261.8932556255318</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-3.81</v>
+        <v>-5.97</v>
       </c>
       <c r="L64" t="n">
-        <v>4.03</v>
+        <v>6.88</v>
       </c>
       <c r="M64" t="n">
         <v>0.67</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.34</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46232.38541666666</v>
+        <v>46232.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>251.35</v>
+        <v>265.55</v>
       </c>
       <c r="I65" t="n">
         <v>259.8855106163474</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K65" t="n">
-        <v>2.95</v>
+        <v>-2.53</v>
       </c>
       <c r="L65" t="n">
         <v>3.07</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>268.3</v>
+        <v>252.55</v>
       </c>
       <c r="I66" t="n">
         <v>254.640104445315</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K66" t="n">
-        <v>1.04</v>
+        <v>-4.9</v>
       </c>
       <c r="L66" t="n">
-        <v>5.42</v>
+        <v>5.84</v>
       </c>
       <c r="M66" t="n">
         <v>0.51</v>
       </c>
       <c r="N66" t="n">
-        <v>2.09</v>
+        <v>7.19</v>
       </c>
       <c r="O66" t="n">
         <v>7.16</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>10.32</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46308.55208333334</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>212.02</v>
+        <v>215.08</v>
       </c>
       <c r="I67" t="n">
         <v>213.2239890901563</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>67.16666666666667</v>
+        <v>68</v>
       </c>
       <c r="K67" t="n">
-        <v>16.05</v>
+        <v>14.84</v>
       </c>
       <c r="L67" t="n">
         <v>6.91</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.86</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>208.45</v>
+        <v>201.95</v>
       </c>
       <c r="I68" t="n">
         <v>204.9786469995923</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.08</v>
+        <v>-6.1</v>
       </c>
       <c r="L68" t="n">
-        <v>5.11</v>
+        <v>6.3</v>
       </c>
       <c r="M68" t="n">
         <v>0.25</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>10</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.8</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="11">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.05</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.01</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>45.76</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.15</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.57</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.63</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7512,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.49</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.01</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.77</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
